--- a/tests/fixtures/01_simple_invoice/01_simple_invoice_pattern-from-local.xlsx
+++ b/tests/fixtures/01_simple_invoice/01_simple_invoice_pattern-from-local.xlsx
@@ -718,7 +718,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>INV-\d+</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
